--- a/week-2/Day_3/Ex2A_events_normalized.xlsx
+++ b/week-2/Day_3/Ex2A_events_normalized.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasaiahantonio\Documents\DataAnalyticsYearUp\week-2\Day_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD22E4D-065C-4EAD-9DA8-E938C94DF24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5247D539-55A2-469A-B0C5-CFB333EE11FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="1" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
   <sheets>
     <sheet name="events_sample" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="134">
   <si>
     <t>Event ID</t>
   </si>
@@ -425,7 +426,7 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Primary Key: Category Code</t>
+    <t>Column1</t>
   </si>
   <si>
     <t>Primary Key: Event ID</t>
@@ -1003,7 +1004,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{35C6E6CA-5EE9-49F2-A9BE-0A99CF598081}" name="Category Code"/>
     <tableColumn id="2" xr3:uid="{067B9D17-B834-44A2-A308-A60B9EDD7A2F}" name="Event Category"/>
-    <tableColumn id="3" xr3:uid="{DF6FDE7B-B25F-4BA9-910B-96F4000DC9DC}" name="Primary Key: Category Code"/>
+    <tableColumn id="3" xr3:uid="{DF6FDE7B-B25F-4BA9-910B-96F4000DC9DC}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1045,6 +1046,20 @@
     <tableColumn id="3" xr3:uid="{800EB217-2D98-4523-937F-3665039F5E20}" name="Venue Contact Name"/>
     <tableColumn id="4" xr3:uid="{6FED6B04-C384-4A16-A57F-51D3B6D34F0F}" name="Venue Email"/>
     <tableColumn id="5" xr3:uid="{AF593160-D459-4491-A10F-68CDAD4D22B5}" name="Venue Phone"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{3C5809AE-6511-4C66-B0A6-97B3CBB9A5DD}" name="Table610" displayName="Table610" ref="A1:E10" totalsRowShown="0">
+  <autoFilter ref="A1:E10" xr:uid="{3C5809AE-6511-4C66-B0A6-97B3CBB9A5DD}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7E1D3082-C83B-4417-8A1F-52679D135666}" name="Venue Location"/>
+    <tableColumn id="2" xr3:uid="{2130D373-5B38-4171-B083-932BF35337E8}" name="Venue ID"/>
+    <tableColumn id="3" xr3:uid="{BEF9D1F8-DC52-4312-A523-6F13A42DDD75}" name="Venue Contact Name"/>
+    <tableColumn id="4" xr3:uid="{068992FD-26B1-42C7-B9F7-A7082DDFD6E1}" name="Venue Email"/>
+    <tableColumn id="5" xr3:uid="{13147103-21DA-4EF5-827C-6B0F16949B1C}" name="Venue Phone"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2657,6 +2672,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E7AB3C-60ED-4B37-A3D1-3B507C4F7532}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
